--- a/settings/data/BossRoutine.xlsx
+++ b/settings/data/BossRoutine.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="11630"/>
+    <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="keine_routine" sheetId="1" r:id="rId1"/>

--- a/settings/data/BossRoutine.xlsx
+++ b/settings/data/BossRoutine.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\10709\Desktop\thloo\settings\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C8B666B-4994-4607-8D31-5B43C7D3B742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080"/>
+    <workbookView xWindow="1440" yWindow="4425" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="keine_routine" sheetId="1" r:id="rId1"/>
@@ -28,6 +34,9 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -355,14 +364,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="24">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -385,150 +388,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="4"/>
       <name val="宋体"/>
@@ -542,8 +401,15 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -552,198 +418,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.05"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -766,251 +446,9 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1043,68 +481,24 @@
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="keine"/>
@@ -1133,7 +527,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Enemy"/>
@@ -1167,7 +561,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="d4c"/>
@@ -1201,8 +595,11 @@
 </file>
 
 <file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="d4c"/>
     </sheetNames>
@@ -1468,32 +865,32 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="20.2181818181818" style="3" customWidth="1"/>
+    <col min="1" max="1" width="20.25" style="3" customWidth="1"/>
     <col min="2" max="2" width="74" style="3" customWidth="1"/>
-    <col min="3" max="3" width="17.7818181818182" style="3" customWidth="1"/>
-    <col min="4" max="4" width="15.2181818181818" style="3" customWidth="1"/>
-    <col min="5" max="6" width="20.4454545454545" style="3" customWidth="1"/>
+    <col min="3" max="3" width="17.75" style="3" customWidth="1"/>
+    <col min="4" max="4" width="15.25" style="3" customWidth="1"/>
+    <col min="5" max="6" width="20.5" style="3" customWidth="1"/>
     <col min="7" max="9" width="25" style="3" customWidth="1"/>
-    <col min="10" max="10" width="38.2181818181818" style="3" customWidth="1"/>
-    <col min="11" max="11" width="20.2181818181818" style="4" customWidth="1"/>
-    <col min="12" max="12" width="20.2181818181818" style="3" customWidth="1"/>
-    <col min="13" max="13" width="18.8909090909091" style="3" customWidth="1"/>
-    <col min="14" max="14" width="20.7818181818182" style="3" customWidth="1"/>
-    <col min="15" max="15" width="16.2181818181818" style="4" customWidth="1"/>
-    <col min="16" max="16" width="20.2181818181818" style="3" customWidth="1"/>
+    <col min="10" max="10" width="38.25" style="3" customWidth="1"/>
+    <col min="11" max="11" width="20.25" style="4" customWidth="1"/>
+    <col min="12" max="12" width="20.25" style="3" customWidth="1"/>
+    <col min="13" max="13" width="18.875" style="3" customWidth="1"/>
+    <col min="14" max="14" width="20.75" style="3" customWidth="1"/>
+    <col min="15" max="15" width="16.25" style="4" customWidth="1"/>
+    <col min="16" max="16" width="20.25" style="3" customWidth="1"/>
     <col min="17" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:16">
+    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1543,7 +940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="151" spans="1:16">
+    <row r="2" spans="1:16" s="1" customFormat="1" ht="128.25" x14ac:dyDescent="0.15">
       <c r="A2" s="5" t="s">
         <v>5</v>
       </c>
@@ -1593,7 +990,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:16">
+    <row r="3" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>21</v>
       </c>
@@ -1643,7 +1040,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A4" s="3" t="str">
         <f>"brou_"&amp;MID(C4,6,999)&amp;"_"&amp;D4</f>
         <v>brou_keine_ns1_1</v>
@@ -1684,7 +1081,7 @@
         <v>enm_keine_ns1_1</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A5" s="3" t="str">
         <f>"brou_"&amp;MID(C5,6,999)&amp;"_"&amp;D5</f>
         <v>brou_keine_ns1_2</v>
@@ -1725,7 +1122,7 @@
         <v>enm_keine_ns1_2</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A6" s="3" t="str">
         <f t="shared" ref="A6:A16" si="0">"brou_"&amp;MID(C6,6,999)&amp;"_"&amp;D6</f>
         <v>brou_keine_ns1_3</v>
@@ -1766,7 +1163,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A7" s="3" t="str">
         <f t="shared" si="0"/>
         <v>brou_keine_sc1_1</v>
@@ -1810,7 +1207,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A8" s="3" t="str">
         <f t="shared" ref="A8" si="1">"brou_"&amp;MID(C8,6,999)&amp;"_"&amp;D8</f>
         <v>brou_keine_sc1_2</v>
@@ -1855,7 +1252,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A9" s="3" t="str">
         <f t="shared" si="0"/>
         <v>brou_keine_sc1_3</v>
@@ -1896,7 +1293,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A10" s="3" t="str">
         <f t="shared" si="0"/>
         <v>brou_keine_sc1_4</v>
@@ -1937,7 +1334,7 @@
         <v>enm_keine_sc1_1</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A11" s="3" t="str">
         <f t="shared" si="0"/>
         <v>brou_keine_sc1_5</v>
@@ -1978,7 +1375,7 @@
         <v>enm_keine_sc1_2</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A12" s="3" t="str">
         <f t="shared" si="0"/>
         <v>brou_keine_ns2_1</v>
@@ -2019,7 +1416,7 @@
         <v>brou_keine_ns2_2</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A13" s="3" t="str">
         <f t="shared" si="0"/>
         <v>brou_keine_ns2_2</v>
@@ -2051,7 +1448,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" s="2" customFormat="1" spans="1:16">
+    <row r="14" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="str">
         <f t="shared" si="0"/>
         <v>brou_keine_ns2_3</v>
@@ -2071,7 +1468,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="2">
-        <f t="shared" ref="F14:P14" si="2">F12</f>
+        <f t="shared" ref="F14:O14" si="2">F12</f>
         <v>18</v>
       </c>
       <c r="G14" s="2">
@@ -2097,7 +1494,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="15" s="2" customFormat="1" spans="1:16">
+    <row r="15" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="str">
         <f t="shared" si="0"/>
         <v>brou_keine_ns2_4</v>
@@ -2133,7 +1530,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A16" s="3" t="str">
         <f t="shared" si="0"/>
         <v>brou_keine_sc2_4</v>
@@ -2171,8 +1568,8 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>